--- a/output-app/BUKU BESAR 2026.xlsx
+++ b/output-app/BUKU BESAR 2026.xlsx
@@ -5,7 +5,13 @@
   <sheets>
     <sheet name="11.01.00" sheetId="1" r:id="rId1"/>
     <sheet name="13.01.00" sheetId="2" r:id="rId2"/>
-    <sheet name="81.02.50" sheetId="3" r:id="rId3"/>
+    <sheet name="15.01.00" sheetId="3" r:id="rId3"/>
+    <sheet name="15.03.00" sheetId="4" r:id="rId4"/>
+    <sheet name="50.01.00" sheetId="5" r:id="rId5"/>
+    <sheet name="50.01.01" sheetId="6" r:id="rId6"/>
+    <sheet name="71.01.00" sheetId="7" r:id="rId7"/>
+    <sheet name="81.02.50" sheetId="8" r:id="rId8"/>
+    <sheet name="97.06.20" sheetId="9" r:id="rId9"/>
   </sheets>
 </workbook>
 </file>
@@ -407,7 +413,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F20"/>
   <cols>
     <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="40.83203125" customWidth="1"/>
@@ -559,22 +565,22 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>18 Mei 2026</v>
+        <v>02 Jan 2001</v>
       </c>
       <c r="B8" t="str">
-        <v>Penerimaan Rek Air (KOPERASI)</v>
+        <v>Bayar: Pembayaran Biaya Perpanjangan STNK Mobil Pick Up KH 1234 PU</v>
       </c>
       <c r="C8" t="str">
         <v>JPK</v>
       </c>
-      <c r="D8">
-        <v>79000</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+      <c r="E8">
+        <v>200000</v>
       </c>
       <c r="F8">
-        <v>79000</v>
+        <v>-200000</v>
       </c>
     </row>
     <row r="9">
@@ -582,19 +588,19 @@
         <v>18 Mei 2026</v>
       </c>
       <c r="B9" t="str">
-        <v>Penerimaan Rek Air (LOKET CABANG)</v>
+        <v>Penerimaan Rek Air (KOPERASI)</v>
       </c>
       <c r="C9" t="str">
         <v>JPK</v>
       </c>
       <c r="D9">
-        <v>361700</v>
+        <v>79000</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9">
-        <v>440700</v>
+        <v>-121000</v>
       </c>
     </row>
     <row r="10">
@@ -602,19 +608,19 @@
         <v>18 Mei 2026</v>
       </c>
       <c r="B10" t="str">
-        <v>Penerimaan Rek Air (LOKET KANTOR)</v>
+        <v>Penerimaan Rek Air (LOKET CABANG)</v>
       </c>
       <c r="C10" t="str">
         <v>JPK</v>
       </c>
       <c r="D10">
-        <v>302900</v>
+        <v>361700</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10">
-        <v>743600</v>
+        <v>240700</v>
       </c>
     </row>
     <row r="11">
@@ -622,19 +628,19 @@
         <v>18 Mei 2026</v>
       </c>
       <c r="B11" t="str">
-        <v>Penerimaan Rek Air (KOPERASI)</v>
+        <v>Penerimaan Rek Air (LOKET KANTOR)</v>
       </c>
       <c r="C11" t="str">
         <v>JPK</v>
       </c>
       <c r="D11">
-        <v>79000</v>
+        <v>302900</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11">
-        <v>822600</v>
+        <v>543600</v>
       </c>
     </row>
     <row r="12">
@@ -642,19 +648,19 @@
         <v>18 Mei 2026</v>
       </c>
       <c r="B12" t="str">
-        <v>Penerimaan Rek Air (LOKET CABANG)</v>
+        <v>Penerimaan Rek Air (KOPERASI)</v>
       </c>
       <c r="C12" t="str">
         <v>JPK</v>
       </c>
       <c r="D12">
-        <v>361700</v>
+        <v>79000</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12">
-        <v>1184300</v>
+        <v>622600</v>
       </c>
     </row>
     <row r="13">
@@ -662,19 +668,19 @@
         <v>18 Mei 2026</v>
       </c>
       <c r="B13" t="str">
-        <v>Penerimaan Rek Air (LOKET KANTOR)</v>
+        <v>Penerimaan Rek Air (LOKET CABANG)</v>
       </c>
       <c r="C13" t="str">
         <v>JPK</v>
       </c>
       <c r="D13">
-        <v>302900</v>
+        <v>361700</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13">
-        <v>1487200</v>
+        <v>984300</v>
       </c>
     </row>
     <row r="14">
@@ -682,19 +688,19 @@
         <v>18 Mei 2026</v>
       </c>
       <c r="B14" t="str">
-        <v>Penerimaan Rek Air (KOPERASI)</v>
+        <v>Penerimaan Rek Air (LOKET KANTOR)</v>
       </c>
       <c r="C14" t="str">
         <v>JPK</v>
       </c>
       <c r="D14">
-        <v>79000</v>
+        <v>302900</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14">
-        <v>1566200</v>
+        <v>1287200</v>
       </c>
     </row>
     <row r="15">
@@ -702,19 +708,19 @@
         <v>18 Mei 2026</v>
       </c>
       <c r="B15" t="str">
-        <v>Penerimaan Rek Air (LOKET CABANG)</v>
+        <v>Penerimaan Rek Air (KOPERASI)</v>
       </c>
       <c r="C15" t="str">
         <v>JPK</v>
       </c>
       <c r="D15">
-        <v>361700</v>
+        <v>79000</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15">
-        <v>1927900</v>
+        <v>1366200</v>
       </c>
     </row>
     <row r="16">
@@ -722,64 +728,104 @@
         <v>18 Mei 2026</v>
       </c>
       <c r="B16" t="str">
-        <v>Penerimaan Rek Air (LOKET KANTOR)</v>
+        <v>Penerimaan Rek Air (LOKET CABANG)</v>
       </c>
       <c r="C16" t="str">
         <v>JPK</v>
       </c>
       <c r="D16">
-        <v>302900</v>
+        <v>361700</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16">
-        <v>2230800</v>
+        <v>1727900</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v/>
+        <v>18 Mei 2026</v>
       </c>
       <c r="B17" t="str">
-        <v/>
+        <v>Penerimaan Rek Air (LOKET KANTOR)</v>
       </c>
       <c r="C17" t="str">
-        <v/>
-      </c>
-      <c r="D17" t="str">
-        <v/>
+        <v>JPK</v>
+      </c>
+      <c r="D17">
+        <v>302900</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
-      <c r="F17" t="str">
-        <v/>
+      <c r="F17">
+        <v>2030800</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
+        <v>21 Jan 2001</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Bayar: Pembayaran Belanja Bahan Habis Pakai Tawas dll</v>
+      </c>
+      <c r="C18" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D18" t="str">
+        <v/>
+      </c>
+      <c r="E18">
+        <v>125000</v>
+      </c>
+      <c r="F18">
+        <v>1905800</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v/>
+      </c>
+      <c r="B19" t="str">
+        <v/>
+      </c>
+      <c r="C19" t="str">
+        <v/>
+      </c>
+      <c r="D19" t="str">
+        <v/>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
         <v>JUMLAH MUTASI</v>
       </c>
-      <c r="B18" t="str">
-        <v/>
-      </c>
-      <c r="C18" t="str">
-        <v/>
-      </c>
-      <c r="D18">
+      <c r="B20" t="str">
+        <v/>
+      </c>
+      <c r="C20" t="str">
+        <v/>
+      </c>
+      <c r="D20">
         <v>2230800</v>
       </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>2230800</v>
+      <c r="E20">
+        <v>325000</v>
+      </c>
+      <c r="F20">
+        <v>1905800</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F20"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1165,6 +1211,1181 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F11"/>
+  <cols>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" customWidth="1"/>
+    <col min="6" max="6" width="18.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>PERUSAHAAN DAERAH AIR MINUM</v>
+      </c>
+      <c r="B1" t="str">
+        <v/>
+      </c>
+      <c r="C1" t="str">
+        <v/>
+      </c>
+      <c r="D1" t="str">
+        <v/>
+      </c>
+      <c r="E1" t="str">
+        <v/>
+      </c>
+      <c r="F1" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>KABUPATEN SERUYAN</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>BUKU BESAR</v>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Nama Perk : Persediaan Bahan Kimia</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v>Kode Perkiraan : 15.01.00</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v/>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Tgl</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Uraian</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Ref.</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Mutasi</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v>Saldo Akhir</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v/>
+      </c>
+      <c r="B7" t="str">
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v>Debet</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Kredit</v>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>01 Jan 2026</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Persediaan Bahan Kimia &amp; BBM</v>
+      </c>
+      <c r="C8" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D8">
+        <v>644</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>21 Jan 2001</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Voucher: Pembayaran Belanja Bahan Habis Pakai Tawas dll</v>
+      </c>
+      <c r="C9" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D9">
+        <v>125000</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9">
+        <v>125644</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v/>
+      </c>
+      <c r="B10" t="str">
+        <v/>
+      </c>
+      <c r="C10" t="str">
+        <v/>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>JUMLAH MUTASI</v>
+      </c>
+      <c r="B11" t="str">
+        <v/>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11">
+        <v>125644</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>125644</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F11"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F10"/>
+  <cols>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" customWidth="1"/>
+    <col min="6" max="6" width="18.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>PERUSAHAAN DAERAH AIR MINUM</v>
+      </c>
+      <c r="B1" t="str">
+        <v/>
+      </c>
+      <c r="C1" t="str">
+        <v/>
+      </c>
+      <c r="D1" t="str">
+        <v/>
+      </c>
+      <c r="E1" t="str">
+        <v/>
+      </c>
+      <c r="F1" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>KABUPATEN SERUYAN</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>BUKU BESAR</v>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Nama Perk : Persediaan Bahan Instalasi</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v>Kode Perkiraan : 15.03.00</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v/>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Tgl</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Uraian</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Ref.</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Mutasi</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v>Saldo Akhir</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v/>
+      </c>
+      <c r="B7" t="str">
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v>Debet</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Kredit</v>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>01 Jan 2026</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Persediaan Bahan Instalasi (Asesoris &amp; Water Meter)</v>
+      </c>
+      <c r="C8" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D8">
+        <v>21696230000.277004</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8">
+        <v>21696230000.28</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v/>
+      </c>
+      <c r="B9" t="str">
+        <v/>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>JUMLAH MUTASI</v>
+      </c>
+      <c r="B10" t="str">
+        <v/>
+      </c>
+      <c r="C10" t="str">
+        <v/>
+      </c>
+      <c r="D10">
+        <v>21696230000.277004</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>21696230000.28</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F10"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F12"/>
+  <cols>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" customWidth="1"/>
+    <col min="6" max="6" width="18.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>PERUSAHAAN DAERAH AIR MINUM</v>
+      </c>
+      <c r="B1" t="str">
+        <v/>
+      </c>
+      <c r="C1" t="str">
+        <v/>
+      </c>
+      <c r="D1" t="str">
+        <v/>
+      </c>
+      <c r="E1" t="str">
+        <v/>
+      </c>
+      <c r="F1" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>KABUPATEN SERUYAN</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>BUKU BESAR</v>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Nama Perk : Utang Usaha</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v>Kode Perkiraan : 50.01.00</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v/>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Tgl</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Uraian</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Ref.</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Mutasi</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v>Saldo Akhir</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v/>
+      </c>
+      <c r="B7" t="str">
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v>Debet</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Kredit</v>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>02 Jan 2001</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Voucher: Pembayaran Biaya Perpanjangan STNK Mobil Pick Up KH 1234 PU</v>
+      </c>
+      <c r="C8" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+      <c r="E8">
+        <v>200000</v>
+      </c>
+      <c r="F8">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>02 Jan 2001</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Bayar: Pembayaran Biaya Perpanjangan STNK Mobil Pick Up KH 1234 PU</v>
+      </c>
+      <c r="C9" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D9">
+        <v>200000</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>21 Jan 2001</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Bayar: Pembayaran Belanja Bahan Habis Pakai Tawas dll</v>
+      </c>
+      <c r="C10" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D10">
+        <v>125000</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10">
+        <v>-125000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v/>
+      </c>
+      <c r="B11" t="str">
+        <v/>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>JUMLAH MUTASI</v>
+      </c>
+      <c r="B12" t="str">
+        <v/>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12">
+        <v>325000</v>
+      </c>
+      <c r="E12">
+        <v>200000</v>
+      </c>
+      <c r="F12">
+        <v>-125000</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F12"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F10"/>
+  <cols>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" customWidth="1"/>
+    <col min="6" max="6" width="18.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>PERUSAHAAN DAERAH AIR MINUM</v>
+      </c>
+      <c r="B1" t="str">
+        <v/>
+      </c>
+      <c r="C1" t="str">
+        <v/>
+      </c>
+      <c r="D1" t="str">
+        <v/>
+      </c>
+      <c r="E1" t="str">
+        <v/>
+      </c>
+      <c r="F1" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>KABUPATEN SERUYAN</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>BUKU BESAR</v>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Nama Perk : Utang Usaha - Bahan Kimia</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v>Kode Perkiraan : 50.01.01</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v/>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Tgl</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Uraian</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Ref.</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Mutasi</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v>Saldo Akhir</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v/>
+      </c>
+      <c r="B7" t="str">
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v>Debet</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Kredit</v>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>21 Jan 2001</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Voucher: Pembayaran Belanja Bahan Habis Pakai Tawas dll</v>
+      </c>
+      <c r="C8" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+      <c r="E8">
+        <v>125000</v>
+      </c>
+      <c r="F8">
+        <v>125000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v/>
+      </c>
+      <c r="B9" t="str">
+        <v/>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>JUMLAH MUTASI</v>
+      </c>
+      <c r="B10" t="str">
+        <v/>
+      </c>
+      <c r="C10" t="str">
+        <v/>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>125000</v>
+      </c>
+      <c r="F10">
+        <v>125000</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F10"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F11"/>
+  <cols>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" customWidth="1"/>
+    <col min="6" max="6" width="18.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>PERUSAHAAN DAERAH AIR MINUM</v>
+      </c>
+      <c r="B1" t="str">
+        <v/>
+      </c>
+      <c r="C1" t="str">
+        <v/>
+      </c>
+      <c r="D1" t="str">
+        <v/>
+      </c>
+      <c r="E1" t="str">
+        <v/>
+      </c>
+      <c r="F1" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>KABUPATEN SERUYAN</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>BUKU BESAR</v>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Nama Perk : Kekayaan Pemda Yang Dipisahkan</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v>Kode Perkiraan : 71.01.00</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v/>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Tgl</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Uraian</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Ref.</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Mutasi</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v>Saldo Akhir</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v/>
+      </c>
+      <c r="B7" t="str">
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v>Debet</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Kredit</v>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>01 Jan 2026</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Persediaan Bahan Instalasi (Asesoris &amp; Water Meter)</v>
+      </c>
+      <c r="C8" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+      <c r="E8">
+        <v>21696230000.277004</v>
+      </c>
+      <c r="F8">
+        <v>21696230000.28</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>01 Jan 2026</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Persediaan Bahan Kimia &amp; BBM</v>
+      </c>
+      <c r="C9" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9">
+        <v>644</v>
+      </c>
+      <c r="F9">
+        <v>21696230644.28</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v/>
+      </c>
+      <c r="B10" t="str">
+        <v/>
+      </c>
+      <c r="C10" t="str">
+        <v/>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>JUMLAH MUTASI</v>
+      </c>
+      <c r="B11" t="str">
+        <v/>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>21696230644.277004</v>
+      </c>
+      <c r="F11">
+        <v>21696230644.28</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F11"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F18"/>
   <cols>
     <col min="1" max="1" width="15.83203125" customWidth="1"/>
@@ -1540,4 +2761,223 @@
     <ignoredError numberStoredAsText="1" sqref="A1:F18"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F10"/>
+  <cols>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" customWidth="1"/>
+    <col min="6" max="6" width="18.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>PERUSAHAAN DAERAH AIR MINUM</v>
+      </c>
+      <c r="B1" t="str">
+        <v/>
+      </c>
+      <c r="C1" t="str">
+        <v/>
+      </c>
+      <c r="D1" t="str">
+        <v/>
+      </c>
+      <c r="E1" t="str">
+        <v/>
+      </c>
+      <c r="F1" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>KABUPATEN SERUYAN</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>BUKU BESAR</v>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Nama Perk : Pemeliharaan Kendaraan</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v>Kode Perkiraan : 97.06.20</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v/>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Tgl</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Uraian</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Ref.</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Mutasi</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v>Saldo Akhir</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v/>
+      </c>
+      <c r="B7" t="str">
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v>Debet</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Kredit</v>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>02 Jan 2001</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Voucher: Pembayaran Biaya Perpanjangan STNK Mobil Pick Up KH 1234 PU</v>
+      </c>
+      <c r="C8" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D8">
+        <v>200000</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v/>
+      </c>
+      <c r="B9" t="str">
+        <v/>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>JUMLAH MUTASI</v>
+      </c>
+      <c r="B10" t="str">
+        <v/>
+      </c>
+      <c r="C10" t="str">
+        <v/>
+      </c>
+      <c r="D10">
+        <v>200000</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>200000</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F10"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/output-app/BUKU BESAR 2026.xlsx
+++ b/output-app/BUKU BESAR 2026.xlsx
@@ -10,8 +10,9 @@
     <sheet name="50.01.00" sheetId="5" r:id="rId5"/>
     <sheet name="50.01.01" sheetId="6" r:id="rId6"/>
     <sheet name="71.01.00" sheetId="7" r:id="rId7"/>
-    <sheet name="81.02.50" sheetId="8" r:id="rId8"/>
-    <sheet name="97.06.20" sheetId="9" r:id="rId9"/>
+    <sheet name="81.01.10" sheetId="8" r:id="rId8"/>
+    <sheet name="81.02.50" sheetId="9" r:id="rId9"/>
+    <sheet name="97.06.20" sheetId="10" r:id="rId10"/>
   </sheets>
 </workbook>
 </file>
@@ -40,7 +41,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="9">
+  <numFmts count="10">
     <numFmt numFmtId="5" formatCode="&quot;$&quot;#,##0_);\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="7" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
@@ -50,6 +51,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -413,7 +415,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F39"/>
   <cols>
     <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="40.83203125" customWidth="1"/>
@@ -585,62 +587,62 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>18 Mei 2026</v>
+        <v>02 Jan 2001</v>
       </c>
       <c r="B9" t="str">
-        <v>Penerimaan Rek Air (KOPERASI)</v>
+        <v>Bayar: Pembayaran Biaya Perpanjangan STNK Mobil Pick Up KH 1234 PU</v>
       </c>
       <c r="C9" t="str">
         <v>JPK</v>
       </c>
-      <c r="D9">
-        <v>79000</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9">
+        <v>200000</v>
       </c>
       <c r="F9">
-        <v>-121000</v>
+        <v>-400000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>18 Mei 2026</v>
+        <v>02 Jan 2001</v>
       </c>
       <c r="B10" t="str">
-        <v>Penerimaan Rek Air (LOKET CABANG)</v>
+        <v>Bayar: Pembayaran Biaya Perpanjangan STNK Mobil Pick Up KH 1234 PU</v>
       </c>
       <c r="C10" t="str">
         <v>JPK</v>
       </c>
-      <c r="D10">
-        <v>361700</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10">
+        <v>200000</v>
       </c>
       <c r="F10">
-        <v>240700</v>
+        <v>-600000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>18 Mei 2026</v>
+        <v>02 Jan 2001</v>
       </c>
       <c r="B11" t="str">
-        <v>Penerimaan Rek Air (LOKET KANTOR)</v>
+        <v>Bayar: Pembayaran Biaya Perpanjangan STNK Mobil Pick Up KH 1234 PU</v>
       </c>
       <c r="C11" t="str">
         <v>JPK</v>
       </c>
-      <c r="D11">
-        <v>302900</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11">
+        <v>200000</v>
       </c>
       <c r="F11">
-        <v>543600</v>
+        <v>-800000</v>
       </c>
     </row>
     <row r="12">
@@ -660,7 +662,7 @@
         <v/>
       </c>
       <c r="F12">
-        <v>622600</v>
+        <v>-721000</v>
       </c>
     </row>
     <row r="13">
@@ -680,7 +682,7 @@
         <v/>
       </c>
       <c r="F13">
-        <v>984300</v>
+        <v>-359300</v>
       </c>
     </row>
     <row r="14">
@@ -700,7 +702,7 @@
         <v/>
       </c>
       <c r="F14">
-        <v>1287200</v>
+        <v>-56400</v>
       </c>
     </row>
     <row r="15">
@@ -720,7 +722,7 @@
         <v/>
       </c>
       <c r="F15">
-        <v>1366200</v>
+        <v>22600</v>
       </c>
     </row>
     <row r="16">
@@ -740,7 +742,7 @@
         <v/>
       </c>
       <c r="F16">
-        <v>1727900</v>
+        <v>384300</v>
       </c>
     </row>
     <row r="17">
@@ -760,77 +762,1375 @@
         <v/>
       </c>
       <c r="F17">
-        <v>2030800</v>
+        <v>687200</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>21 Jan 2001</v>
+        <v>18 Mei 2026</v>
       </c>
       <c r="B18" t="str">
-        <v>Bayar: Pembayaran Belanja Bahan Habis Pakai Tawas dll</v>
+        <v>Penerimaan Rek Air (KOPERASI)</v>
       </c>
       <c r="C18" t="str">
         <v>JPK</v>
       </c>
-      <c r="D18" t="str">
-        <v/>
-      </c>
-      <c r="E18">
-        <v>125000</v>
+      <c r="D18">
+        <v>79000</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
       </c>
       <c r="F18">
-        <v>1905800</v>
+        <v>766200</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v/>
+        <v>18 Mei 2026</v>
       </c>
       <c r="B19" t="str">
-        <v/>
+        <v>Penerimaan Rek Air (LOKET CABANG)</v>
       </c>
       <c r="C19" t="str">
-        <v/>
-      </c>
-      <c r="D19" t="str">
-        <v/>
+        <v>JPK</v>
+      </c>
+      <c r="D19">
+        <v>361700</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
-      <c r="F19" t="str">
-        <v/>
+      <c r="F19">
+        <v>1127900</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Penerimaan Rek Air (LOKET KANTOR)</v>
+      </c>
+      <c r="C20" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D20">
+        <v>302900</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20">
+        <v>1430800</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Penerimaan Rek Air (KOPERASI)</v>
+      </c>
+      <c r="C21" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D21">
+        <v>79000</v>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21">
+        <v>1509800</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Penerimaan Rek Air (LOKET CABANG)</v>
+      </c>
+      <c r="C22" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D22">
+        <v>361700</v>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22">
+        <v>1871500</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Penerimaan Rek Air (LOKET KANTOR)</v>
+      </c>
+      <c r="C23" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D23">
+        <v>302900</v>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23">
+        <v>2174400</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Penerimaan Rek Air (KOPERASI)</v>
+      </c>
+      <c r="C24" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D24">
+        <v>79000</v>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24">
+        <v>2253400</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Penerimaan Rek Air (LOKET CABANG)</v>
+      </c>
+      <c r="C25" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D25">
+        <v>361700</v>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25">
+        <v>2615100</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Penerimaan Rek Air (LOKET KANTOR)</v>
+      </c>
+      <c r="C26" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D26">
+        <v>302900</v>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26">
+        <v>2918000</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Penerimaan Rek Air (KOPERASI)</v>
+      </c>
+      <c r="C27" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D27">
+        <v>79000</v>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27">
+        <v>2997000</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Penerimaan Rek Air (LOKET CABANG)</v>
+      </c>
+      <c r="C28" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D28">
+        <v>361700</v>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28">
+        <v>3358700</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Penerimaan Rek Air (LOKET KANTOR)</v>
+      </c>
+      <c r="C29" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D29">
+        <v>302900</v>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29">
+        <v>3661600</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Penerimaan Rek Air (KOPERASI)</v>
+      </c>
+      <c r="C30" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D30">
+        <v>79000</v>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30">
+        <v>3740600</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Penerimaan Rek Air (LOKET CABANG)</v>
+      </c>
+      <c r="C31" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D31">
+        <v>361700</v>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31">
+        <v>4102300</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Penerimaan Rek Air (LOKET KANTOR)</v>
+      </c>
+      <c r="C32" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D32">
+        <v>302900</v>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+      <c r="F32">
+        <v>4405200</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>24 Jul 2026</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Tes Transaksi Terbaru Paling Atas</v>
+      </c>
+      <c r="C33" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D33">
+        <v>500000</v>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33">
+        <v>4905200</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>21 Jan 2001</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Bayar: Pembayaran Belanja Bahan Habis Pakai Tawas dll</v>
+      </c>
+      <c r="C34" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D34" t="str">
+        <v/>
+      </c>
+      <c r="E34">
+        <v>125000</v>
+      </c>
+      <c r="F34">
+        <v>4780200</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>21 Jan 2001</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Bayar: Pembayaran Belanja Bahan Habis Pakai Tawas dll</v>
+      </c>
+      <c r="C35" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D35" t="str">
+        <v/>
+      </c>
+      <c r="E35">
+        <v>125000</v>
+      </c>
+      <c r="F35">
+        <v>4655200</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>21 Jan 2001</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Bayar: Pembayaran Belanja Bahan Habis Pakai Tawas dll</v>
+      </c>
+      <c r="C36" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D36" t="str">
+        <v/>
+      </c>
+      <c r="E36">
+        <v>125000</v>
+      </c>
+      <c r="F36">
+        <v>4530200</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>21 Jan 2001</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Bayar: Pembayaran Belanja Bahan Habis Pakai Tawas dll</v>
+      </c>
+      <c r="C37" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D37" t="str">
+        <v/>
+      </c>
+      <c r="E37">
+        <v>125000</v>
+      </c>
+      <c r="F37">
+        <v>4405200</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v/>
+      </c>
+      <c r="B38" t="str">
+        <v/>
+      </c>
+      <c r="C38" t="str">
+        <v/>
+      </c>
+      <c r="D38" t="str">
+        <v/>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
         <v>JUMLAH MUTASI</v>
       </c>
-      <c r="B20" t="str">
-        <v/>
-      </c>
-      <c r="C20" t="str">
-        <v/>
-      </c>
-      <c r="D20">
-        <v>2230800</v>
-      </c>
-      <c r="E20">
-        <v>325000</v>
-      </c>
-      <c r="F20">
-        <v>1905800</v>
+      <c r="B39" t="str">
+        <v/>
+      </c>
+      <c r="C39" t="str">
+        <v/>
+      </c>
+      <c r="D39">
+        <v>5705200</v>
+      </c>
+      <c r="E39">
+        <v>1300000</v>
+      </c>
+      <c r="F39">
+        <v>4405200</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F20"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F39"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F14"/>
+  <cols>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" customWidth="1"/>
+    <col min="6" max="6" width="18.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>PERUSAHAAN DAERAH AIR MINUM</v>
+      </c>
+      <c r="B1" t="str">
+        <v/>
+      </c>
+      <c r="C1" t="str">
+        <v/>
+      </c>
+      <c r="D1" t="str">
+        <v/>
+      </c>
+      <c r="E1" t="str">
+        <v/>
+      </c>
+      <c r="F1" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>KABUPATEN SERUYAN</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>BUKU BESAR</v>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Nama Perk : Pemeliharaan Kendaraan</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v>Kode Perkiraan : 97.06.20</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v/>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Tgl</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Uraian</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Ref.</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Mutasi</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v>Saldo Akhir</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v/>
+      </c>
+      <c r="B7" t="str">
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v>Debet</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Kredit</v>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>02 Jan 2001</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Voucher: Pembayaran Biaya Perpanjangan STNK Mobil Pick Up KH 1234 PU</v>
+      </c>
+      <c r="C8" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D8">
+        <v>200000</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>02 Jan 2001</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Voucher: Pembayaran Biaya Perpanjangan STNK Mobil Pick Up KH 1234 PU</v>
+      </c>
+      <c r="C9" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D9">
+        <v>200000</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>02 Jan 2001</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Voucher: Pembayaran Biaya Perpanjangan STNK Mobil Pick Up KH 1234 PU</v>
+      </c>
+      <c r="C10" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D10">
+        <v>200000</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>02 Jan 2001</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Voucher: Pembayaran Biaya Perpanjangan STNK Mobil Pick Up KH 1234 PU</v>
+      </c>
+      <c r="C11" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D11">
+        <v>200000</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11">
+        <v>800000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>24 Jul 2026</v>
+      </c>
+      <c r="B12" t="str">
+        <v>PEMBELIAN KAPORIT</v>
+      </c>
+      <c r="C12" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12">
+        <v>800000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v/>
+      </c>
+      <c r="B13" t="str">
+        <v/>
+      </c>
+      <c r="C13" t="str">
+        <v/>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>JUMLAH MUTASI</v>
+      </c>
+      <c r="B14" t="str">
+        <v/>
+      </c>
+      <c r="C14" t="str">
+        <v/>
+      </c>
+      <c r="D14">
+        <v>800000</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>800000</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F14"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F30"/>
+  <cols>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" customWidth="1"/>
+    <col min="6" max="6" width="18.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>PERUSAHAAN DAERAH AIR MINUM</v>
+      </c>
+      <c r="B1" t="str">
+        <v/>
+      </c>
+      <c r="C1" t="str">
+        <v/>
+      </c>
+      <c r="D1" t="str">
+        <v/>
+      </c>
+      <c r="E1" t="str">
+        <v/>
+      </c>
+      <c r="F1" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>KABUPATEN SERUYAN</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>BUKU BESAR</v>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Nama Perk : Piutang Usaha</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v>Kode Perkiraan : 13.01.00</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v/>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Tgl</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Uraian</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Ref.</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Mutasi</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v>Saldo Akhir</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v/>
+      </c>
+      <c r="B7" t="str">
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v>Debet</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Kredit</v>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Penerimaan Rek Air (KOPERASI)</v>
+      </c>
+      <c r="C8" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+      <c r="E8">
+        <v>44500</v>
+      </c>
+      <c r="F8">
+        <v>-44500</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Penerimaan Rek Air (LOKET CABANG)</v>
+      </c>
+      <c r="C9" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9">
+        <v>180850</v>
+      </c>
+      <c r="F9">
+        <v>-225350</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Penerimaan Rek Air (LOKET KANTOR)</v>
+      </c>
+      <c r="C10" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10">
+        <v>156450</v>
+      </c>
+      <c r="F10">
+        <v>-381800</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Penerimaan Rek Air (KOPERASI)</v>
+      </c>
+      <c r="C11" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11">
+        <v>44500</v>
+      </c>
+      <c r="F11">
+        <v>-426300</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Penerimaan Rek Air (LOKET CABANG)</v>
+      </c>
+      <c r="C12" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12">
+        <v>180850</v>
+      </c>
+      <c r="F12">
+        <v>-607150</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Penerimaan Rek Air (LOKET KANTOR)</v>
+      </c>
+      <c r="C13" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+      <c r="E13">
+        <v>156450</v>
+      </c>
+      <c r="F13">
+        <v>-763600</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Penerimaan Rek Air (KOPERASI)</v>
+      </c>
+      <c r="C14" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+      <c r="E14">
+        <v>44500</v>
+      </c>
+      <c r="F14">
+        <v>-808100</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Penerimaan Rek Air (LOKET CABANG)</v>
+      </c>
+      <c r="C15" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+      <c r="E15">
+        <v>180850</v>
+      </c>
+      <c r="F15">
+        <v>-988950</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Penerimaan Rek Air (LOKET KANTOR)</v>
+      </c>
+      <c r="C16" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D16" t="str">
+        <v/>
+      </c>
+      <c r="E16">
+        <v>156450</v>
+      </c>
+      <c r="F16">
+        <v>-1145400</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Penerimaan Rek Air (KOPERASI)</v>
+      </c>
+      <c r="C17" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D17" t="str">
+        <v/>
+      </c>
+      <c r="E17">
+        <v>44500</v>
+      </c>
+      <c r="F17">
+        <v>-1189900</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Penerimaan Rek Air (LOKET CABANG)</v>
+      </c>
+      <c r="C18" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D18" t="str">
+        <v/>
+      </c>
+      <c r="E18">
+        <v>180850</v>
+      </c>
+      <c r="F18">
+        <v>-1370750</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Penerimaan Rek Air (LOKET KANTOR)</v>
+      </c>
+      <c r="C19" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D19" t="str">
+        <v/>
+      </c>
+      <c r="E19">
+        <v>156450</v>
+      </c>
+      <c r="F19">
+        <v>-1527200</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Penerimaan Rek Air (KOPERASI)</v>
+      </c>
+      <c r="C20" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D20" t="str">
+        <v/>
+      </c>
+      <c r="E20">
+        <v>44500</v>
+      </c>
+      <c r="F20">
+        <v>-1571700</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Penerimaan Rek Air (LOKET CABANG)</v>
+      </c>
+      <c r="C21" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D21" t="str">
+        <v/>
+      </c>
+      <c r="E21">
+        <v>180850</v>
+      </c>
+      <c r="F21">
+        <v>-1752550</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Penerimaan Rek Air (LOKET KANTOR)</v>
+      </c>
+      <c r="C22" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D22" t="str">
+        <v/>
+      </c>
+      <c r="E22">
+        <v>156450</v>
+      </c>
+      <c r="F22">
+        <v>-1909000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Penerimaan Rek Air (KOPERASI)</v>
+      </c>
+      <c r="C23" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D23" t="str">
+        <v/>
+      </c>
+      <c r="E23">
+        <v>44500</v>
+      </c>
+      <c r="F23">
+        <v>-1953500</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Penerimaan Rek Air (LOKET CABANG)</v>
+      </c>
+      <c r="C24" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
+      <c r="E24">
+        <v>180850</v>
+      </c>
+      <c r="F24">
+        <v>-2134350</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Penerimaan Rek Air (LOKET KANTOR)</v>
+      </c>
+      <c r="C25" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D25" t="str">
+        <v/>
+      </c>
+      <c r="E25">
+        <v>156450</v>
+      </c>
+      <c r="F25">
+        <v>-2290800</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Penerimaan Rek Air (KOPERASI)</v>
+      </c>
+      <c r="C26" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D26" t="str">
+        <v/>
+      </c>
+      <c r="E26">
+        <v>44500</v>
+      </c>
+      <c r="F26">
+        <v>-2335300</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Penerimaan Rek Air (LOKET CABANG)</v>
+      </c>
+      <c r="C27" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D27" t="str">
+        <v/>
+      </c>
+      <c r="E27">
+        <v>180850</v>
+      </c>
+      <c r="F27">
+        <v>-2516150</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Penerimaan Rek Air (LOKET KANTOR)</v>
+      </c>
+      <c r="C28" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D28" t="str">
+        <v/>
+      </c>
+      <c r="E28">
+        <v>156450</v>
+      </c>
+      <c r="F28">
+        <v>-2672600</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v/>
+      </c>
+      <c r="B29" t="str">
+        <v/>
+      </c>
+      <c r="C29" t="str">
+        <v/>
+      </c>
+      <c r="D29" t="str">
+        <v/>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>JUMLAH MUTASI</v>
+      </c>
+      <c r="B30" t="str">
+        <v/>
+      </c>
+      <c r="C30" t="str">
+        <v/>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>2672600</v>
+      </c>
+      <c r="F30">
+        <v>-2672600</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F30"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F18"/>
   <cols>
@@ -904,7 +2204,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Nama Perk : Piutang Usaha</v>
+        <v>Nama Perk : Persediaan Bahan Kimia</v>
       </c>
       <c r="B4" t="str">
         <v/>
@@ -913,7 +2213,7 @@
         <v/>
       </c>
       <c r="D4" t="str">
-        <v>Kode Perkiraan : 13.01.00</v>
+        <v>Kode Perkiraan : 15.01.00</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -984,182 +2284,182 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>18 Mei 2026</v>
+        <v>01 Jan 2026</v>
       </c>
       <c r="B8" t="str">
-        <v>Penerimaan Rek Air (KOPERASI)</v>
+        <v>Persediaan Bahan Kimia &amp; BBM</v>
       </c>
       <c r="C8" t="str">
         <v>JPK</v>
       </c>
-      <c r="D8" t="str">
-        <v/>
-      </c>
-      <c r="E8">
-        <v>44500</v>
+      <c r="D8">
+        <v>644</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
       </c>
       <c r="F8">
-        <v>-44500</v>
+        <v>644</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>18 Mei 2026</v>
+        <v>01 Jan 2026</v>
       </c>
       <c r="B9" t="str">
-        <v>Penerimaan Rek Air (LOKET CABANG)</v>
+        <v>Persediaan Bahan Kimia &amp; BBM</v>
       </c>
       <c r="C9" t="str">
         <v>JPK</v>
       </c>
-      <c r="D9" t="str">
-        <v/>
-      </c>
-      <c r="E9">
-        <v>180850</v>
+      <c r="D9">
+        <v>644</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
       </c>
       <c r="F9">
-        <v>-225350</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>18 Mei 2026</v>
+        <v>01 Jan 2026</v>
       </c>
       <c r="B10" t="str">
-        <v>Penerimaan Rek Air (LOKET KANTOR)</v>
+        <v>Persediaan Bahan Kimia &amp; BBM</v>
       </c>
       <c r="C10" t="str">
         <v>JPK</v>
       </c>
-      <c r="D10" t="str">
-        <v/>
-      </c>
-      <c r="E10">
-        <v>156450</v>
+      <c r="D10">
+        <v>644</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
       </c>
       <c r="F10">
-        <v>-381800</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>18 Mei 2026</v>
+        <v>01 Jan 2026</v>
       </c>
       <c r="B11" t="str">
-        <v>Penerimaan Rek Air (KOPERASI)</v>
+        <v>Persediaan Bahan Kimia &amp; BBM</v>
       </c>
       <c r="C11" t="str">
         <v>JPK</v>
       </c>
-      <c r="D11" t="str">
-        <v/>
-      </c>
-      <c r="E11">
-        <v>44500</v>
+      <c r="D11">
+        <v>644</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
       </c>
       <c r="F11">
-        <v>-426300</v>
+        <v>2576</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>18 Mei 2026</v>
+        <v>24 Jul 2026</v>
       </c>
       <c r="B12" t="str">
-        <v>Penerimaan Rek Air (LOKET CABANG)</v>
+        <v>PEMBELIAN KAPORIT</v>
       </c>
       <c r="C12" t="str">
         <v>JPK</v>
       </c>
-      <c r="D12" t="str">
-        <v/>
+      <c r="D12">
+        <v>100000</v>
       </c>
       <c r="E12">
-        <v>180850</v>
+        <v>100000</v>
       </c>
       <c r="F12">
-        <v>-607150</v>
+        <v>2576</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>18 Mei 2026</v>
+        <v>21 Jan 2001</v>
       </c>
       <c r="B13" t="str">
-        <v>Penerimaan Rek Air (LOKET KANTOR)</v>
+        <v>Voucher: Pembayaran Belanja Bahan Habis Pakai Tawas dll</v>
       </c>
       <c r="C13" t="str">
         <v>JPK</v>
       </c>
-      <c r="D13" t="str">
-        <v/>
-      </c>
-      <c r="E13">
-        <v>156450</v>
+      <c r="D13">
+        <v>125000</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
       </c>
       <c r="F13">
-        <v>-763600</v>
+        <v>127576</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>18 Mei 2026</v>
+        <v>21 Jan 2001</v>
       </c>
       <c r="B14" t="str">
-        <v>Penerimaan Rek Air (KOPERASI)</v>
+        <v>Voucher: Pembayaran Belanja Bahan Habis Pakai Tawas dll</v>
       </c>
       <c r="C14" t="str">
         <v>JPK</v>
       </c>
-      <c r="D14" t="str">
-        <v/>
-      </c>
-      <c r="E14">
-        <v>44500</v>
+      <c r="D14">
+        <v>125000</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
       </c>
       <c r="F14">
-        <v>-808100</v>
+        <v>252576</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>18 Mei 2026</v>
+        <v>21 Jan 2001</v>
       </c>
       <c r="B15" t="str">
-        <v>Penerimaan Rek Air (LOKET CABANG)</v>
+        <v>Voucher: Pembayaran Belanja Bahan Habis Pakai Tawas dll</v>
       </c>
       <c r="C15" t="str">
         <v>JPK</v>
       </c>
-      <c r="D15" t="str">
-        <v/>
-      </c>
-      <c r="E15">
-        <v>180850</v>
+      <c r="D15">
+        <v>125000</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
       </c>
       <c r="F15">
-        <v>-988950</v>
+        <v>377576</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>18 Mei 2026</v>
+        <v>21 Jan 2001</v>
       </c>
       <c r="B16" t="str">
-        <v>Penerimaan Rek Air (LOKET KANTOR)</v>
+        <v>Voucher: Pembayaran Belanja Bahan Habis Pakai Tawas dll</v>
       </c>
       <c r="C16" t="str">
         <v>JPK</v>
       </c>
-      <c r="D16" t="str">
-        <v/>
-      </c>
-      <c r="E16">
-        <v>156450</v>
+      <c r="D16">
+        <v>125000</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
       </c>
       <c r="F16">
-        <v>-1145400</v>
+        <v>502576</v>
       </c>
     </row>
     <row r="17">
@@ -1193,13 +2493,13 @@
         <v/>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>602576</v>
       </c>
       <c r="E18">
-        <v>1145400</v>
+        <v>100000</v>
       </c>
       <c r="F18">
-        <v>-1145400</v>
+        <v>502576</v>
       </c>
     </row>
   </sheetData>
@@ -1209,9 +2509,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F13"/>
   <cols>
     <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="40.83203125" customWidth="1"/>
@@ -1283,7 +2583,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Nama Perk : Persediaan Bahan Kimia</v>
+        <v>Nama Perk : Persediaan Bahan Instalasi</v>
       </c>
       <c r="B4" t="str">
         <v/>
@@ -1292,7 +2592,7 @@
         <v/>
       </c>
       <c r="D4" t="str">
-        <v>Kode Perkiraan : 15.01.00</v>
+        <v>Kode Perkiraan : 15.03.00</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -1366,89 +2666,1206 @@
         <v>01 Jan 2026</v>
       </c>
       <c r="B8" t="str">
-        <v>Persediaan Bahan Kimia &amp; BBM</v>
+        <v>Persediaan Bahan Instalasi (Asesoris &amp; Water Meter)</v>
       </c>
       <c r="C8" t="str">
         <v>JPK</v>
       </c>
       <c r="D8">
-        <v>644</v>
+        <v>21696230000.277004</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8">
-        <v>644</v>
+        <v>21696230000.28</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>21 Jan 2001</v>
+        <v>01 Jan 2026</v>
       </c>
       <c r="B9" t="str">
-        <v>Voucher: Pembayaran Belanja Bahan Habis Pakai Tawas dll</v>
+        <v>Persediaan Bahan Instalasi (Asesoris &amp; Water Meter)</v>
       </c>
       <c r="C9" t="str">
         <v>JPK</v>
       </c>
       <c r="D9">
-        <v>125000</v>
+        <v>21696230000.277004</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9">
-        <v>125644</v>
+        <v>43392460000.55</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v/>
+        <v>01 Jan 2026</v>
       </c>
       <c r="B10" t="str">
-        <v/>
+        <v>Persediaan Bahan Instalasi (Asesoris &amp; Water Meter)</v>
       </c>
       <c r="C10" t="str">
-        <v/>
-      </c>
-      <c r="D10" t="str">
-        <v/>
+        <v>JPK</v>
+      </c>
+      <c r="D10">
+        <v>21696230000.277004</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
-      <c r="F10" t="str">
-        <v/>
+      <c r="F10">
+        <v>65088690000.83</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
+        <v>01 Jan 2026</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Persediaan Bahan Instalasi (Asesoris &amp; Water Meter)</v>
+      </c>
+      <c r="C11" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D11">
+        <v>21696230000.277004</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11">
+        <v>86784920001.11</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v/>
+      </c>
+      <c r="B12" t="str">
+        <v/>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
         <v>JUMLAH MUTASI</v>
       </c>
-      <c r="B11" t="str">
-        <v/>
-      </c>
-      <c r="C11" t="str">
-        <v/>
-      </c>
-      <c r="D11">
-        <v>125644</v>
-      </c>
-      <c r="E11">
+      <c r="B13" t="str">
+        <v/>
+      </c>
+      <c r="C13" t="str">
+        <v/>
+      </c>
+      <c r="D13">
+        <v>86784920001.10802</v>
+      </c>
+      <c r="E13">
         <v>0</v>
       </c>
-      <c r="F11">
-        <v>125644</v>
+      <c r="F13">
+        <v>86784920001.11</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F13"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F21"/>
+  <cols>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" customWidth="1"/>
+    <col min="6" max="6" width="18.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>PERUSAHAAN DAERAH AIR MINUM</v>
+      </c>
+      <c r="B1" t="str">
+        <v/>
+      </c>
+      <c r="C1" t="str">
+        <v/>
+      </c>
+      <c r="D1" t="str">
+        <v/>
+      </c>
+      <c r="E1" t="str">
+        <v/>
+      </c>
+      <c r="F1" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>KABUPATEN SERUYAN</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>BUKU BESAR</v>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Nama Perk : Utang Usaha</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v>Kode Perkiraan : 50.01.00</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v/>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Tgl</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Uraian</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Ref.</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Mutasi</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v>Saldo Akhir</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v/>
+      </c>
+      <c r="B7" t="str">
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v>Debet</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Kredit</v>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>02 Jan 2001</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Voucher: Pembayaran Biaya Perpanjangan STNK Mobil Pick Up KH 1234 PU</v>
+      </c>
+      <c r="C8" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+      <c r="E8">
+        <v>200000</v>
+      </c>
+      <c r="F8">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>02 Jan 2001</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Bayar: Pembayaran Biaya Perpanjangan STNK Mobil Pick Up KH 1234 PU</v>
+      </c>
+      <c r="C9" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D9">
+        <v>200000</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>02 Jan 2001</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Voucher: Pembayaran Biaya Perpanjangan STNK Mobil Pick Up KH 1234 PU</v>
+      </c>
+      <c r="C10" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10">
+        <v>200000</v>
+      </c>
+      <c r="F10">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>02 Jan 2001</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Bayar: Pembayaran Biaya Perpanjangan STNK Mobil Pick Up KH 1234 PU</v>
+      </c>
+      <c r="C11" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D11">
+        <v>200000</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>02 Jan 2001</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Voucher: Pembayaran Biaya Perpanjangan STNK Mobil Pick Up KH 1234 PU</v>
+      </c>
+      <c r="C12" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12">
+        <v>200000</v>
+      </c>
+      <c r="F12">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>02 Jan 2001</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Bayar: Pembayaran Biaya Perpanjangan STNK Mobil Pick Up KH 1234 PU</v>
+      </c>
+      <c r="C13" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D13">
+        <v>200000</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>02 Jan 2001</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Voucher: Pembayaran Biaya Perpanjangan STNK Mobil Pick Up KH 1234 PU</v>
+      </c>
+      <c r="C14" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+      <c r="E14">
+        <v>200000</v>
+      </c>
+      <c r="F14">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>02 Jan 2001</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Bayar: Pembayaran Biaya Perpanjangan STNK Mobil Pick Up KH 1234 PU</v>
+      </c>
+      <c r="C15" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D15">
+        <v>200000</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>21 Jan 2001</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Bayar: Pembayaran Belanja Bahan Habis Pakai Tawas dll</v>
+      </c>
+      <c r="C16" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D16">
+        <v>125000</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16">
+        <v>-125000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>21 Jan 2001</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Bayar: Pembayaran Belanja Bahan Habis Pakai Tawas dll</v>
+      </c>
+      <c r="C17" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D17">
+        <v>125000</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17">
+        <v>-250000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>21 Jan 2001</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Bayar: Pembayaran Belanja Bahan Habis Pakai Tawas dll</v>
+      </c>
+      <c r="C18" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D18">
+        <v>125000</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18">
+        <v>-375000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>21 Jan 2001</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Bayar: Pembayaran Belanja Bahan Habis Pakai Tawas dll</v>
+      </c>
+      <c r="C19" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D19">
+        <v>125000</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19">
+        <v>-500000</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v/>
+      </c>
+      <c r="B20" t="str">
+        <v/>
+      </c>
+      <c r="C20" t="str">
+        <v/>
+      </c>
+      <c r="D20" t="str">
+        <v/>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>JUMLAH MUTASI</v>
+      </c>
+      <c r="B21" t="str">
+        <v/>
+      </c>
+      <c r="C21" t="str">
+        <v/>
+      </c>
+      <c r="D21">
+        <v>1300000</v>
+      </c>
+      <c r="E21">
+        <v>800000</v>
+      </c>
+      <c r="F21">
+        <v>-500000</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F21"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F13"/>
+  <cols>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" customWidth="1"/>
+    <col min="6" max="6" width="18.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>PERUSAHAAN DAERAH AIR MINUM</v>
+      </c>
+      <c r="B1" t="str">
+        <v/>
+      </c>
+      <c r="C1" t="str">
+        <v/>
+      </c>
+      <c r="D1" t="str">
+        <v/>
+      </c>
+      <c r="E1" t="str">
+        <v/>
+      </c>
+      <c r="F1" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>KABUPATEN SERUYAN</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>BUKU BESAR</v>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Nama Perk : Utang Usaha - Bahan Kimia</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v>Kode Perkiraan : 50.01.01</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v/>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Tgl</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Uraian</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Ref.</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Mutasi</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v>Saldo Akhir</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v/>
+      </c>
+      <c r="B7" t="str">
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v>Debet</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Kredit</v>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>21 Jan 2001</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Voucher: Pembayaran Belanja Bahan Habis Pakai Tawas dll</v>
+      </c>
+      <c r="C8" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+      <c r="E8">
+        <v>125000</v>
+      </c>
+      <c r="F8">
+        <v>125000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>21 Jan 2001</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Voucher: Pembayaran Belanja Bahan Habis Pakai Tawas dll</v>
+      </c>
+      <c r="C9" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9">
+        <v>125000</v>
+      </c>
+      <c r="F9">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>21 Jan 2001</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Voucher: Pembayaran Belanja Bahan Habis Pakai Tawas dll</v>
+      </c>
+      <c r="C10" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10">
+        <v>125000</v>
+      </c>
+      <c r="F10">
+        <v>375000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>21 Jan 2001</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Voucher: Pembayaran Belanja Bahan Habis Pakai Tawas dll</v>
+      </c>
+      <c r="C11" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11">
+        <v>125000</v>
+      </c>
+      <c r="F11">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v/>
+      </c>
+      <c r="B12" t="str">
+        <v/>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>JUMLAH MUTASI</v>
+      </c>
+      <c r="B13" t="str">
+        <v/>
+      </c>
+      <c r="C13" t="str">
+        <v/>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>500000</v>
+      </c>
+      <c r="F13">
+        <v>500000</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F17"/>
+  <cols>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" customWidth="1"/>
+    <col min="6" max="6" width="18.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>PERUSAHAAN DAERAH AIR MINUM</v>
+      </c>
+      <c r="B1" t="str">
+        <v/>
+      </c>
+      <c r="C1" t="str">
+        <v/>
+      </c>
+      <c r="D1" t="str">
+        <v/>
+      </c>
+      <c r="E1" t="str">
+        <v/>
+      </c>
+      <c r="F1" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>KABUPATEN SERUYAN</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>BUKU BESAR</v>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Nama Perk : Kekayaan Pemda Yang Dipisahkan</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v>Kode Perkiraan : 71.01.00</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v/>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Tgl</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Uraian</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Ref.</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Mutasi</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v>Saldo Akhir</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v/>
+      </c>
+      <c r="B7" t="str">
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v>Debet</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Kredit</v>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>01 Jan 2026</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Persediaan Bahan Instalasi (Asesoris &amp; Water Meter)</v>
+      </c>
+      <c r="C8" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+      <c r="E8">
+        <v>21696230000.277004</v>
+      </c>
+      <c r="F8">
+        <v>21696230000.28</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>01 Jan 2026</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Persediaan Bahan Kimia &amp; BBM</v>
+      </c>
+      <c r="C9" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9">
+        <v>644</v>
+      </c>
+      <c r="F9">
+        <v>21696230644.28</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>01 Jan 2026</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Persediaan Bahan Instalasi (Asesoris &amp; Water Meter)</v>
+      </c>
+      <c r="C10" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10">
+        <v>21696230000.277004</v>
+      </c>
+      <c r="F10">
+        <v>43392460644.55</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>01 Jan 2026</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Persediaan Bahan Kimia &amp; BBM</v>
+      </c>
+      <c r="C11" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11">
+        <v>644</v>
+      </c>
+      <c r="F11">
+        <v>43392461288.55</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>01 Jan 2026</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Persediaan Bahan Instalasi (Asesoris &amp; Water Meter)</v>
+      </c>
+      <c r="C12" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12">
+        <v>21696230000.277004</v>
+      </c>
+      <c r="F12">
+        <v>65088691288.83</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>01 Jan 2026</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Persediaan Bahan Kimia &amp; BBM</v>
+      </c>
+      <c r="C13" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+      <c r="E13">
+        <v>644</v>
+      </c>
+      <c r="F13">
+        <v>65088691932.83</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>01 Jan 2026</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Persediaan Bahan Instalasi (Asesoris &amp; Water Meter)</v>
+      </c>
+      <c r="C14" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+      <c r="E14">
+        <v>21696230000.277004</v>
+      </c>
+      <c r="F14">
+        <v>86784921933.11</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>01 Jan 2026</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Persediaan Bahan Kimia &amp; BBM</v>
+      </c>
+      <c r="C15" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+      <c r="E15">
+        <v>644</v>
+      </c>
+      <c r="F15">
+        <v>86784922577.11</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v/>
+      </c>
+      <c r="B16" t="str">
+        <v/>
+      </c>
+      <c r="C16" t="str">
+        <v/>
+      </c>
+      <c r="D16" t="str">
+        <v/>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>JUMLAH MUTASI</v>
+      </c>
+      <c r="B17" t="str">
+        <v/>
+      </c>
+      <c r="C17" t="str">
+        <v/>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>86784922577.10802</v>
+      </c>
+      <c r="F17">
+        <v>86784922577.11</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F17"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F10"/>
   <cols>
@@ -1522,7 +3939,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Nama Perk : Persediaan Bahan Instalasi</v>
+        <v>Nama Perk : Pendapatan Harga Air</v>
       </c>
       <c r="B4" t="str">
         <v/>
@@ -1531,7 +3948,7 @@
         <v/>
       </c>
       <c r="D4" t="str">
-        <v>Kode Perkiraan : 15.03.00</v>
+        <v>Kode Perkiraan : 81.01.10</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -1602,22 +4019,22 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>01 Jan 2026</v>
+        <v>24 Jul 2026</v>
       </c>
       <c r="B8" t="str">
-        <v>Persediaan Bahan Instalasi (Asesoris &amp; Water Meter)</v>
+        <v>Tes Transaksi Terbaru Paling Atas</v>
       </c>
       <c r="C8" t="str">
         <v>JPK</v>
       </c>
-      <c r="D8">
-        <v>21696230000.277004</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+      <c r="E8">
+        <v>500000</v>
       </c>
       <c r="F8">
-        <v>21696230000.28</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="9">
@@ -1651,13 +4068,13 @@
         <v/>
       </c>
       <c r="D10">
-        <v>21696230000.277004</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="F10">
-        <v>21696230000.28</v>
+        <v>500000</v>
       </c>
     </row>
   </sheetData>
@@ -1667,9 +4084,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F30"/>
   <cols>
     <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="40.83203125" customWidth="1"/>
@@ -1741,7 +4158,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Nama Perk : Utang Usaha</v>
+        <v>Nama Perk : Pendapatan Denda</v>
       </c>
       <c r="B4" t="str">
         <v/>
@@ -1750,7 +4167,7 @@
         <v/>
       </c>
       <c r="D4" t="str">
-        <v>Kode Perkiraan : 50.01.00</v>
+        <v>Kode Perkiraan : 81.02.50</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -1821,10 +4238,10 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>02 Jan 2001</v>
+        <v>18 Mei 2026</v>
       </c>
       <c r="B8" t="str">
-        <v>Voucher: Pembayaran Biaya Perpanjangan STNK Mobil Pick Up KH 1234 PU</v>
+        <v>Penerimaan Rek Air (KOPERASI)</v>
       </c>
       <c r="C8" t="str">
         <v>JPK</v>
@@ -1833,1151 +4250,455 @@
         <v/>
       </c>
       <c r="E8">
-        <v>200000</v>
+        <v>34500</v>
       </c>
       <c r="F8">
-        <v>200000</v>
+        <v>34500</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>02 Jan 2001</v>
+        <v>18 Mei 2026</v>
       </c>
       <c r="B9" t="str">
-        <v>Bayar: Pembayaran Biaya Perpanjangan STNK Mobil Pick Up KH 1234 PU</v>
+        <v>Penerimaan Rek Air (LOKET CABANG)</v>
       </c>
       <c r="C9" t="str">
         <v>JPK</v>
       </c>
-      <c r="D9">
-        <v>200000</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9">
+        <v>180850</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>215350</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>21 Jan 2001</v>
+        <v>18 Mei 2026</v>
       </c>
       <c r="B10" t="str">
-        <v>Bayar: Pembayaran Belanja Bahan Habis Pakai Tawas dll</v>
+        <v>Penerimaan Rek Air (LOKET KANTOR)</v>
       </c>
       <c r="C10" t="str">
         <v>JPK</v>
       </c>
-      <c r="D10">
-        <v>125000</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10">
+        <v>146450</v>
       </c>
       <c r="F10">
-        <v>-125000</v>
+        <v>361800</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v/>
+        <v>18 Mei 2026</v>
       </c>
       <c r="B11" t="str">
-        <v/>
+        <v>Penerimaan Rek Air (KOPERASI)</v>
       </c>
       <c r="C11" t="str">
-        <v/>
+        <v>JPK</v>
       </c>
       <c r="D11" t="str">
         <v/>
       </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
+      <c r="E11">
+        <v>34500</v>
+      </c>
+      <c r="F11">
+        <v>396300</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Penerimaan Rek Air (LOKET CABANG)</v>
+      </c>
+      <c r="C12" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12">
+        <v>180850</v>
+      </c>
+      <c r="F12">
+        <v>577150</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Penerimaan Rek Air (LOKET KANTOR)</v>
+      </c>
+      <c r="C13" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+      <c r="E13">
+        <v>146450</v>
+      </c>
+      <c r="F13">
+        <v>723600</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Penerimaan Rek Air (KOPERASI)</v>
+      </c>
+      <c r="C14" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+      <c r="E14">
+        <v>34500</v>
+      </c>
+      <c r="F14">
+        <v>758100</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Penerimaan Rek Air (LOKET CABANG)</v>
+      </c>
+      <c r="C15" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+      <c r="E15">
+        <v>180850</v>
+      </c>
+      <c r="F15">
+        <v>938950</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Penerimaan Rek Air (LOKET KANTOR)</v>
+      </c>
+      <c r="C16" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D16" t="str">
+        <v/>
+      </c>
+      <c r="E16">
+        <v>146450</v>
+      </c>
+      <c r="F16">
+        <v>1085400</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Penerimaan Rek Air (KOPERASI)</v>
+      </c>
+      <c r="C17" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D17" t="str">
+        <v/>
+      </c>
+      <c r="E17">
+        <v>34500</v>
+      </c>
+      <c r="F17">
+        <v>1119900</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Penerimaan Rek Air (LOKET CABANG)</v>
+      </c>
+      <c r="C18" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D18" t="str">
+        <v/>
+      </c>
+      <c r="E18">
+        <v>180850</v>
+      </c>
+      <c r="F18">
+        <v>1300750</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Penerimaan Rek Air (LOKET KANTOR)</v>
+      </c>
+      <c r="C19" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D19" t="str">
+        <v/>
+      </c>
+      <c r="E19">
+        <v>146450</v>
+      </c>
+      <c r="F19">
+        <v>1447200</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Penerimaan Rek Air (KOPERASI)</v>
+      </c>
+      <c r="C20" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D20" t="str">
+        <v/>
+      </c>
+      <c r="E20">
+        <v>34500</v>
+      </c>
+      <c r="F20">
+        <v>1481700</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Penerimaan Rek Air (LOKET CABANG)</v>
+      </c>
+      <c r="C21" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D21" t="str">
+        <v/>
+      </c>
+      <c r="E21">
+        <v>180850</v>
+      </c>
+      <c r="F21">
+        <v>1662550</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Penerimaan Rek Air (LOKET KANTOR)</v>
+      </c>
+      <c r="C22" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D22" t="str">
+        <v/>
+      </c>
+      <c r="E22">
+        <v>146450</v>
+      </c>
+      <c r="F22">
+        <v>1809000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Penerimaan Rek Air (KOPERASI)</v>
+      </c>
+      <c r="C23" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D23" t="str">
+        <v/>
+      </c>
+      <c r="E23">
+        <v>34500</v>
+      </c>
+      <c r="F23">
+        <v>1843500</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Penerimaan Rek Air (LOKET CABANG)</v>
+      </c>
+      <c r="C24" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
+      <c r="E24">
+        <v>180850</v>
+      </c>
+      <c r="F24">
+        <v>2024350</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Penerimaan Rek Air (LOKET KANTOR)</v>
+      </c>
+      <c r="C25" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D25" t="str">
+        <v/>
+      </c>
+      <c r="E25">
+        <v>146450</v>
+      </c>
+      <c r="F25">
+        <v>2170800</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Penerimaan Rek Air (KOPERASI)</v>
+      </c>
+      <c r="C26" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D26" t="str">
+        <v/>
+      </c>
+      <c r="E26">
+        <v>34500</v>
+      </c>
+      <c r="F26">
+        <v>2205300</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Penerimaan Rek Air (LOKET CABANG)</v>
+      </c>
+      <c r="C27" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D27" t="str">
+        <v/>
+      </c>
+      <c r="E27">
+        <v>180850</v>
+      </c>
+      <c r="F27">
+        <v>2386150</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>18 Mei 2026</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Penerimaan Rek Air (LOKET KANTOR)</v>
+      </c>
+      <c r="C28" t="str">
+        <v>JPK</v>
+      </c>
+      <c r="D28" t="str">
+        <v/>
+      </c>
+      <c r="E28">
+        <v>146450</v>
+      </c>
+      <c r="F28">
+        <v>2532600</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v/>
+      </c>
+      <c r="B29" t="str">
+        <v/>
+      </c>
+      <c r="C29" t="str">
+        <v/>
+      </c>
+      <c r="D29" t="str">
+        <v/>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
         <v>JUMLAH MUTASI</v>
       </c>
-      <c r="B12" t="str">
-        <v/>
-      </c>
-      <c r="C12" t="str">
-        <v/>
-      </c>
-      <c r="D12">
-        <v>325000</v>
-      </c>
-      <c r="E12">
-        <v>200000</v>
-      </c>
-      <c r="F12">
-        <v>-125000</v>
+      <c r="B30" t="str">
+        <v/>
+      </c>
+      <c r="C30" t="str">
+        <v/>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>2532600</v>
+      </c>
+      <c r="F30">
+        <v>2532600</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F12"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F10"/>
-  <cols>
-    <col min="1" max="1" width="15.83203125" customWidth="1"/>
-    <col min="2" max="2" width="40.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" customWidth="1"/>
-    <col min="4" max="4" width="15.83203125" customWidth="1"/>
-    <col min="5" max="5" width="15.83203125" customWidth="1"/>
-    <col min="6" max="6" width="18.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>PERUSAHAAN DAERAH AIR MINUM</v>
-      </c>
-      <c r="B1" t="str">
-        <v/>
-      </c>
-      <c r="C1" t="str">
-        <v/>
-      </c>
-      <c r="D1" t="str">
-        <v/>
-      </c>
-      <c r="E1" t="str">
-        <v/>
-      </c>
-      <c r="F1" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>KABUPATEN SERUYAN</v>
-      </c>
-      <c r="B2" t="str">
-        <v/>
-      </c>
-      <c r="C2" t="str">
-        <v/>
-      </c>
-      <c r="D2" t="str">
-        <v/>
-      </c>
-      <c r="E2" t="str">
-        <v/>
-      </c>
-      <c r="F2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>BUKU BESAR</v>
-      </c>
-      <c r="B3" t="str">
-        <v/>
-      </c>
-      <c r="C3" t="str">
-        <v/>
-      </c>
-      <c r="D3" t="str">
-        <v/>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Nama Perk : Utang Usaha - Bahan Kimia</v>
-      </c>
-      <c r="B4" t="str">
-        <v/>
-      </c>
-      <c r="C4" t="str">
-        <v/>
-      </c>
-      <c r="D4" t="str">
-        <v>Kode Perkiraan : 50.01.01</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v/>
-      </c>
-      <c r="B5" t="str">
-        <v/>
-      </c>
-      <c r="C5" t="str">
-        <v/>
-      </c>
-      <c r="D5" t="str">
-        <v/>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Tgl</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Uraian</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Ref.</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Mutasi</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v>Saldo Akhir</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v/>
-      </c>
-      <c r="B7" t="str">
-        <v/>
-      </c>
-      <c r="C7" t="str">
-        <v/>
-      </c>
-      <c r="D7" t="str">
-        <v>Debet</v>
-      </c>
-      <c r="E7" t="str">
-        <v>Kredit</v>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>21 Jan 2001</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Voucher: Pembayaran Belanja Bahan Habis Pakai Tawas dll</v>
-      </c>
-      <c r="C8" t="str">
-        <v>JPK</v>
-      </c>
-      <c r="D8" t="str">
-        <v/>
-      </c>
-      <c r="E8">
-        <v>125000</v>
-      </c>
-      <c r="F8">
-        <v>125000</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v/>
-      </c>
-      <c r="B9" t="str">
-        <v/>
-      </c>
-      <c r="C9" t="str">
-        <v/>
-      </c>
-      <c r="D9" t="str">
-        <v/>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>JUMLAH MUTASI</v>
-      </c>
-      <c r="B10" t="str">
-        <v/>
-      </c>
-      <c r="C10" t="str">
-        <v/>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>125000</v>
-      </c>
-      <c r="F10">
-        <v>125000</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F10"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
-  <cols>
-    <col min="1" max="1" width="15.83203125" customWidth="1"/>
-    <col min="2" max="2" width="40.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" customWidth="1"/>
-    <col min="4" max="4" width="15.83203125" customWidth="1"/>
-    <col min="5" max="5" width="15.83203125" customWidth="1"/>
-    <col min="6" max="6" width="18.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>PERUSAHAAN DAERAH AIR MINUM</v>
-      </c>
-      <c r="B1" t="str">
-        <v/>
-      </c>
-      <c r="C1" t="str">
-        <v/>
-      </c>
-      <c r="D1" t="str">
-        <v/>
-      </c>
-      <c r="E1" t="str">
-        <v/>
-      </c>
-      <c r="F1" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>KABUPATEN SERUYAN</v>
-      </c>
-      <c r="B2" t="str">
-        <v/>
-      </c>
-      <c r="C2" t="str">
-        <v/>
-      </c>
-      <c r="D2" t="str">
-        <v/>
-      </c>
-      <c r="E2" t="str">
-        <v/>
-      </c>
-      <c r="F2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>BUKU BESAR</v>
-      </c>
-      <c r="B3" t="str">
-        <v/>
-      </c>
-      <c r="C3" t="str">
-        <v/>
-      </c>
-      <c r="D3" t="str">
-        <v/>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Nama Perk : Kekayaan Pemda Yang Dipisahkan</v>
-      </c>
-      <c r="B4" t="str">
-        <v/>
-      </c>
-      <c r="C4" t="str">
-        <v/>
-      </c>
-      <c r="D4" t="str">
-        <v>Kode Perkiraan : 71.01.00</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v/>
-      </c>
-      <c r="B5" t="str">
-        <v/>
-      </c>
-      <c r="C5" t="str">
-        <v/>
-      </c>
-      <c r="D5" t="str">
-        <v/>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Tgl</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Uraian</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Ref.</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Mutasi</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v>Saldo Akhir</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v/>
-      </c>
-      <c r="B7" t="str">
-        <v/>
-      </c>
-      <c r="C7" t="str">
-        <v/>
-      </c>
-      <c r="D7" t="str">
-        <v>Debet</v>
-      </c>
-      <c r="E7" t="str">
-        <v>Kredit</v>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>01 Jan 2026</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Persediaan Bahan Instalasi (Asesoris &amp; Water Meter)</v>
-      </c>
-      <c r="C8" t="str">
-        <v>JPK</v>
-      </c>
-      <c r="D8" t="str">
-        <v/>
-      </c>
-      <c r="E8">
-        <v>21696230000.277004</v>
-      </c>
-      <c r="F8">
-        <v>21696230000.28</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>01 Jan 2026</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Persediaan Bahan Kimia &amp; BBM</v>
-      </c>
-      <c r="C9" t="str">
-        <v>JPK</v>
-      </c>
-      <c r="D9" t="str">
-        <v/>
-      </c>
-      <c r="E9">
-        <v>644</v>
-      </c>
-      <c r="F9">
-        <v>21696230644.28</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v/>
-      </c>
-      <c r="B10" t="str">
-        <v/>
-      </c>
-      <c r="C10" t="str">
-        <v/>
-      </c>
-      <c r="D10" t="str">
-        <v/>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>JUMLAH MUTASI</v>
-      </c>
-      <c r="B11" t="str">
-        <v/>
-      </c>
-      <c r="C11" t="str">
-        <v/>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>21696230644.277004</v>
-      </c>
-      <c r="F11">
-        <v>21696230644.28</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F11"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F18"/>
-  <cols>
-    <col min="1" max="1" width="15.83203125" customWidth="1"/>
-    <col min="2" max="2" width="40.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" customWidth="1"/>
-    <col min="4" max="4" width="15.83203125" customWidth="1"/>
-    <col min="5" max="5" width="15.83203125" customWidth="1"/>
-    <col min="6" max="6" width="18.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>PERUSAHAAN DAERAH AIR MINUM</v>
-      </c>
-      <c r="B1" t="str">
-        <v/>
-      </c>
-      <c r="C1" t="str">
-        <v/>
-      </c>
-      <c r="D1" t="str">
-        <v/>
-      </c>
-      <c r="E1" t="str">
-        <v/>
-      </c>
-      <c r="F1" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>KABUPATEN SERUYAN</v>
-      </c>
-      <c r="B2" t="str">
-        <v/>
-      </c>
-      <c r="C2" t="str">
-        <v/>
-      </c>
-      <c r="D2" t="str">
-        <v/>
-      </c>
-      <c r="E2" t="str">
-        <v/>
-      </c>
-      <c r="F2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>BUKU BESAR</v>
-      </c>
-      <c r="B3" t="str">
-        <v/>
-      </c>
-      <c r="C3" t="str">
-        <v/>
-      </c>
-      <c r="D3" t="str">
-        <v/>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Nama Perk : Pendapatan Denda</v>
-      </c>
-      <c r="B4" t="str">
-        <v/>
-      </c>
-      <c r="C4" t="str">
-        <v/>
-      </c>
-      <c r="D4" t="str">
-        <v>Kode Perkiraan : 81.02.50</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v/>
-      </c>
-      <c r="B5" t="str">
-        <v/>
-      </c>
-      <c r="C5" t="str">
-        <v/>
-      </c>
-      <c r="D5" t="str">
-        <v/>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Tgl</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Uraian</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Ref.</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Mutasi</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v>Saldo Akhir</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v/>
-      </c>
-      <c r="B7" t="str">
-        <v/>
-      </c>
-      <c r="C7" t="str">
-        <v/>
-      </c>
-      <c r="D7" t="str">
-        <v>Debet</v>
-      </c>
-      <c r="E7" t="str">
-        <v>Kredit</v>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>18 Mei 2026</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Penerimaan Rek Air (KOPERASI)</v>
-      </c>
-      <c r="C8" t="str">
-        <v>JPK</v>
-      </c>
-      <c r="D8" t="str">
-        <v/>
-      </c>
-      <c r="E8">
-        <v>34500</v>
-      </c>
-      <c r="F8">
-        <v>34500</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>18 Mei 2026</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Penerimaan Rek Air (LOKET CABANG)</v>
-      </c>
-      <c r="C9" t="str">
-        <v>JPK</v>
-      </c>
-      <c r="D9" t="str">
-        <v/>
-      </c>
-      <c r="E9">
-        <v>180850</v>
-      </c>
-      <c r="F9">
-        <v>215350</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>18 Mei 2026</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Penerimaan Rek Air (LOKET KANTOR)</v>
-      </c>
-      <c r="C10" t="str">
-        <v>JPK</v>
-      </c>
-      <c r="D10" t="str">
-        <v/>
-      </c>
-      <c r="E10">
-        <v>146450</v>
-      </c>
-      <c r="F10">
-        <v>361800</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>18 Mei 2026</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Penerimaan Rek Air (KOPERASI)</v>
-      </c>
-      <c r="C11" t="str">
-        <v>JPK</v>
-      </c>
-      <c r="D11" t="str">
-        <v/>
-      </c>
-      <c r="E11">
-        <v>34500</v>
-      </c>
-      <c r="F11">
-        <v>396300</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>18 Mei 2026</v>
-      </c>
-      <c r="B12" t="str">
-        <v>Penerimaan Rek Air (LOKET CABANG)</v>
-      </c>
-      <c r="C12" t="str">
-        <v>JPK</v>
-      </c>
-      <c r="D12" t="str">
-        <v/>
-      </c>
-      <c r="E12">
-        <v>180850</v>
-      </c>
-      <c r="F12">
-        <v>577150</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>18 Mei 2026</v>
-      </c>
-      <c r="B13" t="str">
-        <v>Penerimaan Rek Air (LOKET KANTOR)</v>
-      </c>
-      <c r="C13" t="str">
-        <v>JPK</v>
-      </c>
-      <c r="D13" t="str">
-        <v/>
-      </c>
-      <c r="E13">
-        <v>146450</v>
-      </c>
-      <c r="F13">
-        <v>723600</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>18 Mei 2026</v>
-      </c>
-      <c r="B14" t="str">
-        <v>Penerimaan Rek Air (KOPERASI)</v>
-      </c>
-      <c r="C14" t="str">
-        <v>JPK</v>
-      </c>
-      <c r="D14" t="str">
-        <v/>
-      </c>
-      <c r="E14">
-        <v>34500</v>
-      </c>
-      <c r="F14">
-        <v>758100</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>18 Mei 2026</v>
-      </c>
-      <c r="B15" t="str">
-        <v>Penerimaan Rek Air (LOKET CABANG)</v>
-      </c>
-      <c r="C15" t="str">
-        <v>JPK</v>
-      </c>
-      <c r="D15" t="str">
-        <v/>
-      </c>
-      <c r="E15">
-        <v>180850</v>
-      </c>
-      <c r="F15">
-        <v>938950</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>18 Mei 2026</v>
-      </c>
-      <c r="B16" t="str">
-        <v>Penerimaan Rek Air (LOKET KANTOR)</v>
-      </c>
-      <c r="C16" t="str">
-        <v>JPK</v>
-      </c>
-      <c r="D16" t="str">
-        <v/>
-      </c>
-      <c r="E16">
-        <v>146450</v>
-      </c>
-      <c r="F16">
-        <v>1085400</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v/>
-      </c>
-      <c r="B17" t="str">
-        <v/>
-      </c>
-      <c r="C17" t="str">
-        <v/>
-      </c>
-      <c r="D17" t="str">
-        <v/>
-      </c>
-      <c r="E17" t="str">
-        <v/>
-      </c>
-      <c r="F17" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>JUMLAH MUTASI</v>
-      </c>
-      <c r="B18" t="str">
-        <v/>
-      </c>
-      <c r="C18" t="str">
-        <v/>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18">
-        <v>1085400</v>
-      </c>
-      <c r="F18">
-        <v>1085400</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F18"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F10"/>
-  <cols>
-    <col min="1" max="1" width="15.83203125" customWidth="1"/>
-    <col min="2" max="2" width="40.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" customWidth="1"/>
-    <col min="4" max="4" width="15.83203125" customWidth="1"/>
-    <col min="5" max="5" width="15.83203125" customWidth="1"/>
-    <col min="6" max="6" width="18.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>PERUSAHAAN DAERAH AIR MINUM</v>
-      </c>
-      <c r="B1" t="str">
-        <v/>
-      </c>
-      <c r="C1" t="str">
-        <v/>
-      </c>
-      <c r="D1" t="str">
-        <v/>
-      </c>
-      <c r="E1" t="str">
-        <v/>
-      </c>
-      <c r="F1" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>KABUPATEN SERUYAN</v>
-      </c>
-      <c r="B2" t="str">
-        <v/>
-      </c>
-      <c r="C2" t="str">
-        <v/>
-      </c>
-      <c r="D2" t="str">
-        <v/>
-      </c>
-      <c r="E2" t="str">
-        <v/>
-      </c>
-      <c r="F2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>BUKU BESAR</v>
-      </c>
-      <c r="B3" t="str">
-        <v/>
-      </c>
-      <c r="C3" t="str">
-        <v/>
-      </c>
-      <c r="D3" t="str">
-        <v/>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Nama Perk : Pemeliharaan Kendaraan</v>
-      </c>
-      <c r="B4" t="str">
-        <v/>
-      </c>
-      <c r="C4" t="str">
-        <v/>
-      </c>
-      <c r="D4" t="str">
-        <v>Kode Perkiraan : 97.06.20</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v/>
-      </c>
-      <c r="B5" t="str">
-        <v/>
-      </c>
-      <c r="C5" t="str">
-        <v/>
-      </c>
-      <c r="D5" t="str">
-        <v/>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Tgl</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Uraian</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Ref.</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Mutasi</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v>Saldo Akhir</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v/>
-      </c>
-      <c r="B7" t="str">
-        <v/>
-      </c>
-      <c r="C7" t="str">
-        <v/>
-      </c>
-      <c r="D7" t="str">
-        <v>Debet</v>
-      </c>
-      <c r="E7" t="str">
-        <v>Kredit</v>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>02 Jan 2001</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Voucher: Pembayaran Biaya Perpanjangan STNK Mobil Pick Up KH 1234 PU</v>
-      </c>
-      <c r="C8" t="str">
-        <v>JPK</v>
-      </c>
-      <c r="D8">
-        <v>200000</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8">
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v/>
-      </c>
-      <c r="B9" t="str">
-        <v/>
-      </c>
-      <c r="C9" t="str">
-        <v/>
-      </c>
-      <c r="D9" t="str">
-        <v/>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>JUMLAH MUTASI</v>
-      </c>
-      <c r="B10" t="str">
-        <v/>
-      </c>
-      <c r="C10" t="str">
-        <v/>
-      </c>
-      <c r="D10">
-        <v>200000</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>200000</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F30"/>
   </ignoredErrors>
 </worksheet>
 </file>